--- a/루나.xlsx
+++ b/루나.xlsx
@@ -1,30 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saj08\OneDrive\문서\trpg\아카이브\기록표\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AF9905-1051-49EF-B738-321D3595BC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10450"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="루나" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="65">
   <si>
     <t>x</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -269,13 +280,28 @@
   </si>
   <si>
     <t>루나</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>야수의 정수(패시브)</t>
+  </si>
+  <si>
+    <t>건강 +4, 속도-3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>늑대 리듬 동조</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 속도가 자신보다 빠를 때  받는 쾌락 데미지 +1, 동조 성공 시 매턴마다 1 sp 회복.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
@@ -894,7 +920,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -910,7 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
@@ -931,34 +957,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -973,131 +984,137 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1385,7 +1402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Z57"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1396,947 +1413,951 @@
     <col min="17" max="17" width="20.58203125" customWidth="1"/>
     <col min="18" max="19" width="8.58203125" customWidth="1"/>
     <col min="20" max="20" width="12.58203125" customWidth="1"/>
-    <col min="22" max="22" width="12.58203125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="22.5" style="1" customWidth="1"/>
     <col min="23" max="26" width="8.58203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:21" ht="30.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="65" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="65" t="s">
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="64" t="s">
+      <c r="O2" s="56"/>
+      <c r="P2" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="63" t="s">
+      <c r="Q2" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="61" t="s">
+      <c r="R2" s="46"/>
+      <c r="S2" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="T2" s="61"/>
-      <c r="U2" s="60"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="2:21" ht="30.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="58" t="s">
+      <c r="H3" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="57" t="s">
+      <c r="M3" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="57" t="s">
+      <c r="N3" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="57" t="s">
+      <c r="O3" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="54" t="s">
+      <c r="Q3" s="58"/>
+      <c r="R3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="53" t="s">
+      <c r="S3" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="53" t="s">
+      <c r="T3" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="52" t="s">
+      <c r="U3" s="40" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="18.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="34" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="7">
         <v>30</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="48" t="s">
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="Q4" s="51" t="s">
+      <c r="Q4" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="43">
+      <c r="R4" s="32">
         <f>SUM($C$7:$M$7)*5</f>
         <v>30</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="43">
-        <f>R4+S4-T4</f>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="32">
+        <f t="shared" ref="U4:U15" si="0">R4+S4-T4</f>
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:21" ht="18.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="7">
         <v>30</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="48">
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="37">
         <f>INT(3+(R10/5))</f>
         <v>4</v>
       </c>
-      <c r="Q5" s="45" t="s">
+      <c r="Q5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="32">
         <f>SUM($C$7:$M$7)*5</f>
         <v>30</v>
       </c>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="43">
-        <f>R5+S5-T5</f>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="32">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="18" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="7">
         <v>6</v>
       </c>
-      <c r="D6" s="47">
-        <f>INDEX($D:$D, COLUMN(A1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="47">
-        <f>INDEX($D:$D, COLUMN(B1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="47">
-        <f>INDEX($D:$D, COLUMN(C1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="47">
-        <f>INDEX($D:$D, COLUMN(D1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="47">
-        <f>INDEX($D:$D, COLUMN(E1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="47">
-        <f>INDEX($D:$D, COLUMN(F1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="47">
-        <f>INDEX($D:$D, COLUMN(G1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="47">
-        <f>INDEX($D:$D, COLUMN(H1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="47">
-        <f>INDEX($D:$D, COLUMN(I1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="47">
-        <f>INDEX($D:$D, COLUMN(J1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="47">
-        <f>INDEX($D:$D, COLUMN(K1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="47">
-        <f>INDEX($D:$D, COLUMN(L1)+17)</f>
+      <c r="D6" s="36">
+        <f t="shared" ref="D6:O6" si="1">INDEX($D:$D, COLUMN(A1)+17)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="36">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P6" s="7"/>
-      <c r="Q6" s="45" t="s">
+      <c r="Q6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="R6" s="43">
-        <f>SUM(C6:P6)</f>
+      <c r="R6" s="32">
+        <f t="shared" ref="R6:R15" si="2">SUM(C6:P6)</f>
         <v>6</v>
       </c>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="43">
-        <f>R6+S6-T6</f>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="32">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="34" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="7">
         <v>6</v>
       </c>
       <c r="D7" s="7">
-        <f>INDEX($E:$E, COLUMN(A1)+17)</f>
+        <f t="shared" ref="D7:O7" si="3">INDEX($E:$E, COLUMN(A1)+17)</f>
         <v>0</v>
       </c>
       <c r="E7" s="7">
-        <f>INDEX($E:$E, COLUMN(B1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F7" s="7">
-        <f>INDEX($E:$E, COLUMN(C1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G7" s="7">
-        <f>INDEX($E:$E, COLUMN(D1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H7" s="7">
-        <f>INDEX($E:$E, COLUMN(E1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I7" s="7">
-        <f>INDEX($E:$E, COLUMN(F1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J7" s="7">
-        <f>INDEX($E:$E, COLUMN(G1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K7" s="7">
-        <f>INDEX($E:$E, COLUMN(H1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L7" s="7">
-        <f>INDEX($E:$E, COLUMN(I1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M7" s="7">
-        <f>INDEX($E:$E, COLUMN(J1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N7" s="7">
-        <f>INDEX($E:$E, COLUMN(K1)+17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O7" s="7">
-        <f>INDEX($E:$E, COLUMN(L1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="45" t="s">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="R7" s="43">
-        <f>SUM(C7:P7)</f>
-        <v>6</v>
-      </c>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="43">
-        <f>R7+S7-T7</f>
-        <v>6</v>
+      <c r="R7" s="32">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="32">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="7">
         <v>6</v>
       </c>
       <c r="D8" s="7">
-        <f>INDEX($F:$F, COLUMN(A1)+17)</f>
+        <f t="shared" ref="D8:O8" si="4">INDEX($F:$F, COLUMN(A1)+17)</f>
         <v>0</v>
       </c>
       <c r="E8" s="7">
-        <f>INDEX($F:$F, COLUMN(B1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F8" s="7">
-        <f>INDEX($F:$F, COLUMN(C1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G8" s="7">
-        <f>INDEX($F:$F, COLUMN(D1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H8" s="7">
-        <f>INDEX($F:$F, COLUMN(E1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I8" s="7">
-        <f>INDEX($F:$F, COLUMN(F1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J8" s="7">
-        <f>INDEX($F:$F, COLUMN(G1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K8" s="7">
-        <f>INDEX($F:$F, COLUMN(H1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L8" s="7">
-        <f>INDEX($F:$F, COLUMN(I1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M8" s="7">
-        <f>INDEX($F:$F, COLUMN(J1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N8" s="7">
-        <f>INDEX($F:$F, COLUMN(K1)+17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O8" s="7">
-        <f>INDEX($F:$F, COLUMN(L1)+17)</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="45" t="s">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>-3</v>
+      </c>
+      <c r="Q8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="43">
-        <f>SUM(C8:P8)</f>
-        <v>6</v>
-      </c>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="43">
-        <f>R8+S8-T8</f>
-        <v>6</v>
+      <c r="R8" s="32">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="32">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="7">
         <v>6</v>
       </c>
       <c r="D9" s="7">
-        <f>INDEX($G:$G, COLUMN(A1)+17)</f>
+        <f t="shared" ref="D9:O9" si="5">INDEX($G:$G, COLUMN(A1)+17)</f>
         <v>0</v>
       </c>
       <c r="E9" s="7">
-        <f>INDEX($G:$G, COLUMN(B1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F9" s="7">
-        <f>INDEX($G:$G, COLUMN(C1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G9" s="7">
-        <f>INDEX($G:$G, COLUMN(D1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H9" s="7">
-        <f>INDEX($G:$G, COLUMN(E1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I9" s="7">
-        <f>INDEX($G:$G, COLUMN(F1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J9" s="7">
-        <f>INDEX($G:$G, COLUMN(G1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K9" s="7">
-        <f>INDEX($G:$G, COLUMN(H1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L9" s="7">
-        <f>INDEX($G:$G, COLUMN(I1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M9" s="7">
-        <f>INDEX($G:$G, COLUMN(J1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" s="7">
-        <f>INDEX($G:$G, COLUMN(K1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9" s="7">
-        <f>INDEX($G:$G, COLUMN(L1)+17)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P9" s="7"/>
-      <c r="Q9" s="45" t="s">
+      <c r="Q9" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="43">
-        <f>SUM(C9:P9)</f>
+      <c r="R9" s="32">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="43">
-        <f>R9+S9-T9</f>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="32">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="34" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="7">
-        <f>INDEX($H:$H, COLUMN(A$1)+17)</f>
+        <f t="shared" ref="D10:O10" si="6">INDEX($H:$H, COLUMN(A$1)+17)</f>
         <v>0</v>
       </c>
       <c r="E10" s="7">
-        <f>INDEX($H:$H, COLUMN(B$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F10" s="7">
-        <f>INDEX($H:$H, COLUMN(C$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G10" s="7">
-        <f>INDEX($H:$H, COLUMN(D$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H10" s="7">
-        <f>INDEX($H:$H, COLUMN(E$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I10" s="7">
-        <f>INDEX($H:$H, COLUMN(F$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J10" s="7">
-        <f>INDEX($H:$H, COLUMN(G$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K10" s="7">
-        <f>INDEX($H:$H, COLUMN(H$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L10" s="7">
-        <f>INDEX($H:$H, COLUMN(I$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M10" s="7">
-        <f>INDEX($H:$H, COLUMN(J$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N10" s="7">
-        <f>INDEX($H:$H, COLUMN(K$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O10" s="7">
-        <f>INDEX($H:$H, COLUMN(L$1)+17)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P10" s="7"/>
-      <c r="Q10" s="45" t="s">
+      <c r="Q10" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="R10" s="43">
-        <f>SUM(C10:P10)</f>
-        <v>6</v>
-      </c>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="43">
-        <f>R10+S10-T10</f>
-        <v>6</v>
+      <c r="R10" s="32">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="32">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="7">
         <v>6</v>
       </c>
       <c r="D11" s="7">
-        <f>INDEX($I:$I, COLUMN(A$1)+17)</f>
+        <f t="shared" ref="D11:O11" si="7">INDEX($I:$I, COLUMN(A$1)+17)</f>
         <v>0</v>
       </c>
       <c r="E11" s="7">
-        <f>INDEX($I:$I, COLUMN(B$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F11" s="7">
-        <f>INDEX($I:$I, COLUMN(C$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G11" s="7">
-        <f>INDEX($I:$I, COLUMN(D$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H11" s="7">
-        <f>INDEX($I:$I, COLUMN(E$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I11" s="7">
-        <f>INDEX($I:$I, COLUMN(F$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J11" s="7">
-        <f>INDEX($I:$I, COLUMN(G$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K11" s="7">
-        <f>INDEX($I:$I, COLUMN(H$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L11" s="7">
-        <f>INDEX($I:$I, COLUMN(I$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M11" s="7">
-        <f>INDEX($I:$I, COLUMN(J$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N11" s="7">
-        <f>INDEX($I:$I, COLUMN(K$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O11" s="7">
-        <f>INDEX($I:$I, COLUMN(L$1)+17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P11" s="7"/>
-      <c r="Q11" s="45" t="s">
+      <c r="Q11" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="R11" s="43">
-        <f>SUM(C11:P11)</f>
+      <c r="R11" s="32">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="43">
-        <f>R11+S11-T11</f>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="32">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="34" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12" s="7">
-        <f>INDEX($J:$J, COLUMN(A$1)+17)</f>
+        <f t="shared" ref="D12:O12" si="8">INDEX($J:$J, COLUMN(A$1)+17)</f>
         <v>0</v>
       </c>
       <c r="E12" s="7">
-        <f>INDEX($J:$J, COLUMN(B$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F12" s="7">
-        <f>INDEX($J:$J, COLUMN(C$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G12" s="7">
-        <f>INDEX($J:$J, COLUMN(D$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f>INDEX($J:$J, COLUMN(E$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I12" s="7">
-        <f>INDEX($J:$J, COLUMN(F$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J12" s="7">
-        <f>INDEX($J:$J, COLUMN(G$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K12" s="7">
-        <f>INDEX($J:$J, COLUMN(H$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L12" s="7">
-        <f>INDEX($J:$J, COLUMN(I$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M12" s="7">
-        <f>INDEX($J:$J, COLUMN(J$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N12" s="7">
-        <f>INDEX($J:$J, COLUMN(K$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O12" s="7">
-        <f>INDEX($J:$J, COLUMN(L$1)+17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P12" s="7"/>
-      <c r="Q12" s="45" t="s">
+      <c r="Q12" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="R12" s="43">
-        <f>SUM(C12:P12)</f>
-        <v>6</v>
-      </c>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="43">
-        <f>R12+S12-T12</f>
-        <v>6</v>
+      <c r="R12" s="32">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="32">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="35" t="s">
         <v>0</v>
       </c>
       <c r="D13" s="7">
-        <f>INDEX($K:$K, COLUMN(A$1)+17)</f>
+        <f t="shared" ref="D13:O13" si="9">INDEX($K:$K, COLUMN(A$1)+17)</f>
         <v>0</v>
       </c>
       <c r="E13" s="7">
-        <f>INDEX($K:$K, COLUMN(B$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F13" s="7">
-        <f>INDEX($K:$K, COLUMN(C$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G13" s="7">
-        <f>INDEX($K:$K, COLUMN(D$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H13" s="7">
-        <f>INDEX($K:$K, COLUMN(E$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I13" s="7">
-        <f>INDEX($K:$K, COLUMN(F$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J13" s="7">
-        <f>INDEX($K:$K, COLUMN(G$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K13" s="7">
-        <f>INDEX($K:$K, COLUMN(H$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L13" s="7">
-        <f>INDEX($K:$K, COLUMN(I$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M13" s="7">
-        <f>INDEX($K:$K, COLUMN(J$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N13" s="7">
-        <f>INDEX($K:$K, COLUMN(K$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O13" s="7">
-        <f>INDEX($K:$K, COLUMN(L$1)+17)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P13" s="7"/>
-      <c r="Q13" s="45" t="s">
+      <c r="Q13" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R13" s="43">
-        <f>SUM(C13:P13)</f>
+      <c r="R13" s="32">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="43">
-        <f>R13+S13-T13</f>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="32">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="35" t="s">
         <v>0</v>
       </c>
       <c r="D14" s="7">
-        <f>INDEX($L:$L, COLUMN(A$1)+17)</f>
+        <f t="shared" ref="D14:O14" si="10">INDEX($L:$L, COLUMN(A$1)+17)</f>
         <v>0</v>
       </c>
       <c r="E14" s="7">
-        <f>INDEX($L:$L, COLUMN(B$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F14" s="7">
-        <f>INDEX($L:$L, COLUMN(C$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G14" s="7">
-        <f>INDEX($L:$L, COLUMN(D$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H14" s="7">
-        <f>INDEX($L:$L, COLUMN(E$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I14" s="7">
-        <f>INDEX($L:$L, COLUMN(F$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J14" s="7">
-        <f>INDEX($L:$L, COLUMN(G$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K14" s="7">
-        <f>INDEX($L:$L, COLUMN(H$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L14" s="7">
-        <f>INDEX($L:$L, COLUMN(I$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M14" s="7">
-        <f>INDEX($L:$L, COLUMN(J$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N14" s="7">
-        <f>INDEX($L:$L, COLUMN(K$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O14" s="7">
-        <f>INDEX($L:$L, COLUMN(L$1)+17)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="P14" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Q14" s="45" t="s">
+      <c r="Q14" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="R14" s="43">
-        <f>SUM(C14:P14)</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="44"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="43">
-        <f>R14+S14-T14</f>
+      <c r="R14" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="32">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="34" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D15" s="7">
-        <f>INDEX($M:$M, COLUMN(A$1)+17)</f>
+        <f t="shared" ref="D15:O15" si="11">INDEX($M:$M, COLUMN(A$1)+17)</f>
         <v>0</v>
       </c>
       <c r="E15" s="7">
-        <f>INDEX($M:$M, COLUMN(B$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F15" s="7">
-        <f>INDEX($M:$M, COLUMN(C$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G15" s="7">
-        <f>INDEX($M:$M, COLUMN(D$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <f>INDEX($M:$M, COLUMN(E$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I15" s="7">
-        <f>INDEX($M:$M, COLUMN(F$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J15" s="7">
-        <f>INDEX($M:$M, COLUMN(G$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K15" s="7">
-        <f>INDEX($M:$M, COLUMN(H$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L15" s="7">
-        <f>INDEX($M:$M, COLUMN(I$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M15" s="7">
-        <f>INDEX($M:$M, COLUMN(J$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="N15" s="7">
-        <f>INDEX($M:$M, COLUMN(K$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O15" s="7">
-        <f>INDEX($M:$M, COLUMN(L$1)+17)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="45" t="s">
+      <c r="Q15" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="R15" s="43">
-        <f>SUM(C15:P15)</f>
-        <v>0</v>
-      </c>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="43">
-        <f>R15+S15-T15</f>
+      <c r="R15" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="32">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="17" spans="2:26" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="40" t="s">
+      <c r="C17" s="30"/>
+      <c r="D17" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I17" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="38" t="s">
+      <c r="L17" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="M17" s="39" t="s">
+      <c r="M17" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="N17" s="38" t="s">
+      <c r="N17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="O17" s="37" t="s">
+      <c r="O17" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Q17" s="29" t="s">
+      <c r="Q17" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="R17" s="28" t="s">
+      <c r="R17" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="S17" s="27"/>
-      <c r="T17" s="27"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="26"/>
-      <c r="W17" s="23" t="s">
+      <c r="S17" s="51"/>
+      <c r="T17" s="51"/>
+      <c r="U17" s="51"/>
+      <c r="V17" s="52"/>
+      <c r="W17" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="X17" s="23" t="s">
+      <c r="X17" s="18" t="s">
         <v>40</v>
       </c>
       <c r="Y17"/>
     </row>
     <row r="18" spans="2:26" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="25"/>
-      <c r="C18" s="36" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="10"/>
@@ -2349,66 +2370,66 @@
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="Q18" s="34" t="s">
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="Q18" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="R18" s="33" t="s">
+      <c r="R18" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="32"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="23">
+      <c r="S18" s="63"/>
+      <c r="T18" s="63"/>
+      <c r="U18" s="63"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="18">
         <v>1</v>
       </c>
-      <c r="X18" s="23"/>
+      <c r="X18" s="18"/>
       <c r="Y18"/>
     </row>
     <row r="19" spans="2:26" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="25"/>
-      <c r="C19" s="24" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="Q19" s="34" t="s">
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="Q19" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="R19" s="33" t="s">
+      <c r="R19" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23">
+      <c r="S19" s="63"/>
+      <c r="T19" s="63"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18">
         <v>2</v>
       </c>
       <c r="Y19"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -2417,288 +2438,297 @@
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="26"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="Q20" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="R20" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="52"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
       <c r="Y20"/>
     </row>
     <row r="21" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B21" s="25"/>
-      <c r="C21" s="24" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="51"/>
+      <c r="V21" s="52"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
       <c r="Y21"/>
       <c r="Z21"/>
     </row>
     <row r="22" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B22" s="25"/>
-      <c r="C22" s="24" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="26"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
+      <c r="U22" s="51"/>
+      <c r="V22" s="52"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
       <c r="Y22"/>
       <c r="Z22"/>
     </row>
     <row r="23" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B23" s="25"/>
-      <c r="C23" s="24" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="26"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="51"/>
+      <c r="V23" s="52"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
       <c r="Y23"/>
       <c r="Z23"/>
     </row>
     <row r="24" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B24" s="25"/>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="26"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="50"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
+      <c r="U24" s="51"/>
+      <c r="V24" s="52"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
       <c r="Y24"/>
       <c r="Z24"/>
     </row>
     <row r="25" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B25" s="25"/>
-      <c r="C25" s="24" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="26"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="50"/>
+      <c r="S25" s="51"/>
+      <c r="T25" s="51"/>
+      <c r="U25" s="51"/>
+      <c r="V25" s="52"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
       <c r="Y25"/>
       <c r="Z25"/>
     </row>
     <row r="26" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B26" s="25"/>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="20"/>
+      <c r="C26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="26"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
+      <c r="V26" s="52"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
       <c r="Y26"/>
       <c r="Z26"/>
     </row>
     <row r="27" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B27" s="25"/>
-      <c r="C27" s="24" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18">
+        <v>-1</v>
+      </c>
       <c r="Y27"/>
       <c r="Z27"/>
     </row>
-    <row r="28" spans="2:26" ht="17" x14ac:dyDescent="0.45">
-      <c r="B28" s="30" t="s">
+    <row r="28" spans="2:26" x14ac:dyDescent="0.45">
+      <c r="B28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23">
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18">
         <v>1</v>
       </c>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="26"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="Q28" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="R28" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="52"/>
+      <c r="W28" s="18"/>
       <c r="Y28"/>
       <c r="Z28"/>
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="B29" s="25"/>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
     </row>
     <row r="30" spans="2:26" ht="18" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="31" spans="2:26" ht="18" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="12"/>
-      <c r="G31" s="14" t="s">
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="G31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="12"/>
-      <c r="K31" s="14" t="s">
+      <c r="H31" s="59"/>
+      <c r="I31" s="60"/>
+      <c r="K31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="12"/>
+      <c r="L31" s="59"/>
+      <c r="M31" s="60"/>
       <c r="Q31" s="1"/>
-      <c r="R31" s="21" t="s">
+      <c r="R31" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C32" s="11" t="s">
@@ -2729,16 +2759,16 @@
         <v>11</v>
       </c>
       <c r="Q32" s="1"/>
-      <c r="R32" s="20" t="s">
+      <c r="R32" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="S32" s="20" t="s">
+      <c r="S32" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="T32" s="20" t="s">
+      <c r="T32" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="U32" s="19" t="s">
+      <c r="U32" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2762,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="J33"/>
-      <c r="K33" s="16" t="s">
+      <c r="K33" s="14" t="s">
         <v>10</v>
       </c>
       <c r="L33" s="7">
@@ -2775,16 +2805,16 @@
       <c r="N33"/>
       <c r="O33"/>
       <c r="P33"/>
-      <c r="Q33" s="18" t="s">
+      <c r="Q33" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17">
+      <c r="R33" s="15"/>
+      <c r="S33" s="15">
         <f>U15</f>
         <v>0</v>
       </c>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
     </row>
     <row r="34" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B34" s="2"/>
@@ -2806,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="J34"/>
-      <c r="K34" s="16" t="s">
+      <c r="K34" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L34" s="7">
@@ -2819,16 +2849,16 @@
       <c r="N34"/>
       <c r="O34"/>
       <c r="P34"/>
-      <c r="Q34" s="17" t="s">
+      <c r="Q34" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17">
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15">
         <f>U15</f>
         <v>0</v>
       </c>
-      <c r="U34" s="17"/>
+      <c r="U34" s="15"/>
     </row>
     <row r="35" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="2"/>
@@ -2837,7 +2867,7 @@
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="6">
-        <f>SUM(D35)</f>
+        <f t="shared" ref="E35:E42" si="12">SUM(D35)</f>
         <v>0</v>
       </c>
       <c r="F35"/>
@@ -2846,18 +2876,18 @@
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="6">
-        <f>SUM(H35)</f>
+        <f t="shared" ref="I35:I42" si="13">SUM(H35)</f>
         <v>0</v>
       </c>
       <c r="J35"/>
-      <c r="K35" s="16" t="s">
+      <c r="K35" s="14" t="s">
         <v>8</v>
       </c>
       <c r="L35" s="7">
         <v>6</v>
       </c>
       <c r="M35" s="6">
-        <f>SUM(L35)</f>
+        <f t="shared" ref="M35:M42" si="14">SUM(L35)</f>
         <v>6</v>
       </c>
       <c r="N35"/>
@@ -2876,7 +2906,7 @@
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="6">
-        <f>SUM(D36)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F36"/>
@@ -2885,18 +2915,18 @@
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="6">
-        <f>SUM(H36)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J36"/>
-      <c r="K36" s="16" t="s">
+      <c r="K36" s="14" t="s">
         <v>7</v>
       </c>
       <c r="L36" s="7">
         <v>6</v>
       </c>
       <c r="M36" s="6">
-        <f>SUM(L36)</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="N36"/>
@@ -2915,7 +2945,7 @@
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="6">
-        <f>SUM(D37)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F37"/>
@@ -2924,18 +2954,18 @@
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="6">
-        <f>SUM(H37)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J37"/>
-      <c r="K37" s="16" t="s">
+      <c r="K37" s="14" t="s">
         <v>6</v>
       </c>
       <c r="L37" s="7">
         <v>6</v>
       </c>
       <c r="M37" s="6">
-        <f>SUM(L37)</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="N37"/>
@@ -2954,7 +2984,7 @@
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="6">
-        <f>SUM(D38)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F38"/>
@@ -2963,18 +2993,18 @@
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="6">
-        <f>SUM(H38)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J38"/>
-      <c r="K38" s="16" t="s">
+      <c r="K38" s="14" t="s">
         <v>5</v>
       </c>
       <c r="L38" s="7">
         <v>6</v>
       </c>
       <c r="M38" s="6">
-        <f>SUM(L38)</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="N38"/>
@@ -2993,7 +3023,7 @@
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="6">
-        <f>SUM(D39)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F39"/>
@@ -3002,18 +3032,18 @@
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="6">
-        <f>SUM(H39)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J39"/>
-      <c r="K39" s="16" t="s">
+      <c r="K39" s="14" t="s">
         <v>4</v>
       </c>
       <c r="L39" s="7">
         <v>6</v>
       </c>
       <c r="M39" s="6">
-        <f>SUM(L39)</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="N39"/>
@@ -3032,7 +3062,7 @@
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="6">
-        <f>SUM(D40)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F40"/>
@@ -3041,18 +3071,18 @@
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="6">
-        <f>SUM(H40)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J40"/>
-      <c r="K40" s="16" t="s">
+      <c r="K40" s="14" t="s">
         <v>3</v>
       </c>
       <c r="L40" s="7">
         <v>6</v>
       </c>
       <c r="M40" s="6">
-        <f>SUM(L40)</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="N40"/>
@@ -3071,7 +3101,7 @@
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="6">
-        <f>SUM(D41)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F41"/>
@@ -3080,18 +3110,18 @@
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="6">
-        <f>SUM(H41)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J41"/>
-      <c r="K41" s="16" t="s">
+      <c r="K41" s="14" t="s">
         <v>2</v>
       </c>
       <c r="L41" s="7">
         <v>6</v>
       </c>
       <c r="M41" s="6">
-        <f>SUM(L41)</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="N41"/>
@@ -3110,7 +3140,7 @@
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="3">
-        <f>SUM(D42)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F42"/>
@@ -3119,18 +3149,18 @@
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="3">
-        <f>SUM(H42)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J42"/>
-      <c r="K42" s="15" t="s">
+      <c r="K42" s="13" t="s">
         <v>1</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M42" s="3">
-        <f>SUM(L42)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N42"/>
@@ -3166,13 +3196,13 @@
     </row>
     <row r="44" spans="2:21" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B44" s="2"/>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="12"/>
+      <c r="E44" s="60"/>
       <c r="F44"/>
       <c r="G44"/>
       <c r="H44"/>
@@ -3285,7 +3315,7 @@
         <v>8</v>
       </c>
       <c r="E48" s="6">
-        <f>SUM(D48)</f>
+        <f t="shared" ref="E48:E55" si="15">SUM(D48)</f>
         <v>8</v>
       </c>
       <c r="F48"/>
@@ -3314,7 +3344,7 @@
         <v>7</v>
       </c>
       <c r="E49" s="6">
-        <f>SUM(D49)</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="F49"/>
@@ -3343,7 +3373,7 @@
         <v>4</v>
       </c>
       <c r="E50" s="6">
-        <f>SUM(D50)</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="F50"/>
@@ -3372,7 +3402,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="6">
-        <f>SUM(D51)</f>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="F51"/>
@@ -3401,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="E52" s="6">
-        <f>SUM(D52)</f>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="F52"/>
@@ -3430,7 +3460,7 @@
         <v>2</v>
       </c>
       <c r="E53" s="6">
-        <f>SUM(D53)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="F53"/>
@@ -3459,7 +3489,7 @@
         <v>4</v>
       </c>
       <c r="E54" s="6">
-        <f>SUM(D54)</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="F54"/>
@@ -3488,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="3">
-        <f>SUM(D55)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F55"/>
@@ -3554,6 +3584,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="R28:V28"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="R31:U31"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="R26:V26"/>
     <mergeCell ref="R27:V27"/>
     <mergeCell ref="D4:O5"/>
@@ -3567,16 +3606,7 @@
     <mergeCell ref="R23:V23"/>
     <mergeCell ref="R24:V24"/>
     <mergeCell ref="R25:V25"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="R31:U31"/>
-    <mergeCell ref="D44:E44"/>
     <mergeCell ref="S2:U2"/>
-    <mergeCell ref="R28:V28"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="R18:V18"/>
-    <mergeCell ref="R19:V19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
